--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,37 +2422,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R18" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,17 +2492,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,28 +2511,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2537,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,50 +2545,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R19" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,17 +2602,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,12 +2621,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B6" t="n">
         <v>78937</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R6" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B7" t="n">
         <v>78937</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R7" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B6" t="n">
         <v>78937</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R6" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B7" t="n">
         <v>78937</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R7" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130448983</v>
       </c>
       <c r="B3" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130446098</v>
       </c>
       <c r="B4" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>130446099</v>
       </c>
       <c r="B6" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130448984</v>
       </c>
       <c r="B7" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>130446102</v>
       </c>
       <c r="B8" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>130448980</v>
       </c>
       <c r="B9" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130446103</v>
       </c>
       <c r="B10" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>130448986</v>
       </c>
       <c r="B12" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130448987</v>
       </c>
       <c r="B13" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>130448988</v>
       </c>
       <c r="B14" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>130446100</v>
       </c>
       <c r="B15" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130448979</v>
       </c>
       <c r="B16" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>130448985</v>
       </c>
       <c r="B17" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,50 +2422,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R18" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,17 +2479,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,12 +2498,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2534,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,37 +2548,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R19" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,17 +2618,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,28 +2637,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
         <v>130446089</v>
       </c>
       <c r="B20" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B3" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R3" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130446098</v>
+        <v>130448983</v>
       </c>
       <c r="B4" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509854</v>
+        <v>510086</v>
       </c>
       <c r="R4" t="n">
-        <v>6956341</v>
+        <v>6956190</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B6" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R6" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B7" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R7" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,7 +1339,7 @@
         <v>130446102</v>
       </c>
       <c r="B8" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>130448980</v>
       </c>
       <c r="B9" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130446103</v>
       </c>
       <c r="B10" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>130448986</v>
       </c>
       <c r="B12" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130448987</v>
       </c>
       <c r="B13" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>130448988</v>
       </c>
       <c r="B14" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>130446100</v>
       </c>
       <c r="B15" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130448979</v>
       </c>
       <c r="B16" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>130448985</v>
       </c>
       <c r="B17" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>130446110</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>130448981</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>130446089</v>
       </c>
       <c r="B20" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130446098</v>
+        <v>130446109</v>
       </c>
       <c r="B3" t="n">
-        <v>78966</v>
+        <v>91755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,26 +798,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509854</v>
+        <v>509892</v>
       </c>
       <c r="R3" t="n">
-        <v>6956341</v>
+        <v>6956310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +880,21 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B4" t="n">
         <v>78966</v>
@@ -931,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R4" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130446109</v>
+        <v>130448983</v>
       </c>
       <c r="B5" t="n">
-        <v>91754</v>
+        <v>78966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,30 +1029,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509892</v>
+        <v>510086</v>
       </c>
       <c r="R5" t="n">
-        <v>6956310</v>
+        <v>6956190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,21 +1107,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130446109</v>
       </c>
       <c r="B3" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130446098</v>
+        <v>130448983</v>
       </c>
       <c r="B4" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509854</v>
+        <v>510086</v>
       </c>
       <c r="R4" t="n">
-        <v>6956341</v>
+        <v>6956190</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B5" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R5" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B6" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R6" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B7" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R7" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,7 +1339,7 @@
         <v>130446102</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>130448980</v>
       </c>
       <c r="B9" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130446103</v>
       </c>
       <c r="B10" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>130448986</v>
       </c>
       <c r="B12" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130448987</v>
       </c>
       <c r="B13" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>130448988</v>
       </c>
       <c r="B14" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>130446100</v>
       </c>
       <c r="B15" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130448979</v>
       </c>
       <c r="B16" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>130448985</v>
       </c>
       <c r="B17" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>58013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,37 +2422,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R18" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,17 +2492,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,28 +2511,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2537,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B19" t="n">
-        <v>58011</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,50 +2545,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R19" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,17 +2602,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,12 +2621,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
         <v>130446089</v>
       </c>
       <c r="B20" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130446109</v>
+        <v>130448983</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,30 +798,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509892</v>
+        <v>510086</v>
       </c>
       <c r="R3" t="n">
-        <v>6956310</v>
+        <v>6956190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,21 +876,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B4" t="n">
         <v>78968</v>
@@ -950,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R4" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130446098</v>
+        <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>91757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,26 +1010,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509854</v>
+        <v>509892</v>
       </c>
       <c r="R5" t="n">
-        <v>6956341</v>
+        <v>6956310</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,6 +1092,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B18" t="n">
-        <v>58013</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,50 +2422,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R18" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,17 +2479,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,12 +2498,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2534,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>58013</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,37 +2548,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R19" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,17 +2618,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,28 +2637,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130448983</v>
+        <v>130446109</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,26 +798,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510086</v>
+        <v>509892</v>
       </c>
       <c r="R3" t="n">
-        <v>6956190</v>
+        <v>6956310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,6 +880,21 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -999,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130446109</v>
+        <v>130448983</v>
       </c>
       <c r="B5" t="n">
-        <v>91757</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,30 +1029,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509892</v>
+        <v>510086</v>
       </c>
       <c r="R5" t="n">
-        <v>6956310</v>
+        <v>6956190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,21 +1107,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B6" t="n">
         <v>78968</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R6" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B7" t="n">
         <v>78968</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R7" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>58013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,37 +2422,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R18" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,17 +2492,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,28 +2511,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2537,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B19" t="n">
-        <v>58013</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,50 +2545,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R19" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,17 +2602,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,12 +2621,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130446102</v>
+        <v>130448980</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>79801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510080</v>
+        <v>510014</v>
       </c>
       <c r="R8" t="n">
-        <v>6956202</v>
+        <v>6956212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130448980</v>
+        <v>130446102</v>
       </c>
       <c r="B9" t="n">
-        <v>79801</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510014</v>
+        <v>510080</v>
       </c>
       <c r="R9" t="n">
-        <v>6956212</v>
+        <v>6956202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B18" t="n">
-        <v>58013</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,50 +2422,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R18" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,17 +2479,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,12 +2498,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2534,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>58013</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,37 +2548,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R19" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,17 +2618,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,28 +2637,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130446109</v>
+        <v>130448983</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,30 +798,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509892</v>
+        <v>510086</v>
       </c>
       <c r="R3" t="n">
-        <v>6956310</v>
+        <v>6956190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,21 +876,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1018,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130448983</v>
+        <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>91757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,26 +1010,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510086</v>
+        <v>509892</v>
       </c>
       <c r="R5" t="n">
-        <v>6956190</v>
+        <v>6956310</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,6 +1092,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B6" t="n">
         <v>78968</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R6" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B7" t="n">
         <v>78968</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R7" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>58013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,37 +2422,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R18" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,17 +2492,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,28 +2511,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2537,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B19" t="n">
-        <v>58013</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,50 +2545,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R19" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,17 +2602,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,12 +2621,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130448983</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130446098</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>130446099</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130448984</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130448980</v>
+        <v>130446102</v>
       </c>
       <c r="B8" t="n">
-        <v>79801</v>
+        <v>78976</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510014</v>
+        <v>510080</v>
       </c>
       <c r="R8" t="n">
-        <v>6956212</v>
+        <v>6956202</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130446102</v>
+        <v>130448980</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>79809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510080</v>
+        <v>510014</v>
       </c>
       <c r="R9" t="n">
-        <v>6956202</v>
+        <v>6956212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,7 +1551,7 @@
         <v>130446103</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>130448986</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130448987</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>130448988</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>130446100</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130448979</v>
       </c>
       <c r="B16" t="n">
-        <v>79801</v>
+        <v>79809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>130448985</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>130448981</v>
       </c>
       <c r="B18" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>130446110</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>130446089</v>
       </c>
       <c r="B20" t="n">
-        <v>79801</v>
+        <v>79809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B3" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R3" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130446098</v>
+        <v>130448983</v>
       </c>
       <c r="B4" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509854</v>
+        <v>510086</v>
       </c>
       <c r="R4" t="n">
-        <v>6956341</v>
+        <v>6956190</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B6" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R6" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B7" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R7" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,7 +1339,7 @@
         <v>130446102</v>
       </c>
       <c r="B8" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>130448980</v>
       </c>
       <c r="B9" t="n">
-        <v>79809</v>
+        <v>79810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130446103</v>
       </c>
       <c r="B10" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83199</v>
+        <v>83200</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>130448986</v>
       </c>
       <c r="B12" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130448987</v>
       </c>
       <c r="B13" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>130448988</v>
       </c>
       <c r="B14" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>130446100</v>
       </c>
       <c r="B15" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130448979</v>
       </c>
       <c r="B16" t="n">
-        <v>79809</v>
+        <v>79810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>130448985</v>
       </c>
       <c r="B17" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>130448981</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>130446110</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>130446089</v>
       </c>
       <c r="B20" t="n">
-        <v>79809</v>
+        <v>79810</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130446098</v>
+        <v>130446109</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>91772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,26 +798,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509854</v>
+        <v>509892</v>
       </c>
       <c r="R3" t="n">
-        <v>6956341</v>
+        <v>6956310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +880,21 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R4" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130446109</v>
+        <v>130448983</v>
       </c>
       <c r="B5" t="n">
-        <v>91771</v>
+        <v>78978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,30 +1029,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509892</v>
+        <v>510086</v>
       </c>
       <c r="R5" t="n">
-        <v>6956310</v>
+        <v>6956190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,21 +1107,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
         <v>130448984</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130446099</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>130446102</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>130448980</v>
       </c>
       <c r="B9" t="n">
-        <v>79810</v>
+        <v>79811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130446103</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130448977</v>
       </c>
       <c r="B11" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>130448986</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130448987</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>130448988</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>130446100</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130448979</v>
       </c>
       <c r="B16" t="n">
-        <v>79810</v>
+        <v>79811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>130448985</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B18" t="n">
-        <v>58022</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,50 +2422,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R18" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,17 +2479,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,12 +2498,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2534,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,37 +2548,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R19" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,17 +2618,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,28 +2637,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
         <v>130446089</v>
       </c>
       <c r="B20" t="n">
-        <v>79810</v>
+        <v>79811</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130448984</v>
+        <v>130446099</v>
       </c>
       <c r="B6" t="n">
         <v>78978</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510208</v>
+        <v>509927</v>
       </c>
       <c r="R6" t="n">
-        <v>6956132</v>
+        <v>6956285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130446099</v>
+        <v>130448984</v>
       </c>
       <c r="B7" t="n">
         <v>78978</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509927</v>
+        <v>510208</v>
       </c>
       <c r="R7" t="n">
-        <v>6956285</v>
+        <v>6956132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130446098</v>
+        <v>130448983</v>
       </c>
       <c r="B4" t="n">
         <v>78978</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509854</v>
+        <v>510086</v>
       </c>
       <c r="R4" t="n">
-        <v>6956341</v>
+        <v>6956190</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B5" t="n">
         <v>78978</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R5" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130446102</v>
+        <v>130448980</v>
       </c>
       <c r="B8" t="n">
-        <v>78978</v>
+        <v>79811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510080</v>
+        <v>510014</v>
       </c>
       <c r="R8" t="n">
-        <v>6956202</v>
+        <v>6956212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130448980</v>
+        <v>130446102</v>
       </c>
       <c r="B9" t="n">
-        <v>79811</v>
+        <v>78978</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510014</v>
+        <v>510080</v>
       </c>
       <c r="R9" t="n">
-        <v>6956212</v>
+        <v>6956202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,37 +2422,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R18" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,17 +2492,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,28 +2511,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2537,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,50 +2545,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R19" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,17 +2602,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,12 +2621,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130446109</v>
+        <v>130448983</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>78978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,30 +798,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509892</v>
+        <v>510086</v>
       </c>
       <c r="R3" t="n">
-        <v>6956310</v>
+        <v>6956190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,21 +876,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130448983</v>
+        <v>130446098</v>
       </c>
       <c r="B4" t="n">
         <v>78978</v>
@@ -950,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510086</v>
+        <v>509854</v>
       </c>
       <c r="R4" t="n">
-        <v>6956190</v>
+        <v>6956341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130446098</v>
+        <v>130446109</v>
       </c>
       <c r="B5" t="n">
-        <v>78978</v>
+        <v>91772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,26 +1010,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509854</v>
+        <v>509892</v>
       </c>
       <c r="R5" t="n">
-        <v>6956341</v>
+        <v>6956310</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,6 +1092,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130448980</v>
+        <v>130446102</v>
       </c>
       <c r="B8" t="n">
-        <v>79811</v>
+        <v>78978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510014</v>
+        <v>510080</v>
       </c>
       <c r="R8" t="n">
-        <v>6956212</v>
+        <v>6956202</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130446102</v>
+        <v>130448980</v>
       </c>
       <c r="B9" t="n">
-        <v>78978</v>
+        <v>79811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510080</v>
+        <v>510014</v>
       </c>
       <c r="R9" t="n">
-        <v>6956202</v>
+        <v>6956212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2411,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130448981</v>
+        <v>130446110</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,50 +2422,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510001</v>
+        <v>509881</v>
       </c>
       <c r="R18" t="n">
-        <v>6956229</v>
+        <v>6956321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,17 +2479,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,12 +2498,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2534,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446110</v>
+        <v>130448981</v>
       </c>
       <c r="B19" t="n">
-        <v>79221</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,37 +2548,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509881</v>
+        <v>510001</v>
       </c>
       <c r="R19" t="n">
-        <v>6956321</v>
+        <v>6956229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,17 +2618,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,28 +2637,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1330874</v>
+        <v>130446109</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sidsjö, Jmt</t>
+          <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510174.1682879571</v>
+        <v>509892</v>
       </c>
       <c r="R2" t="n">
-        <v>6956138.545426289</v>
+        <v>6956310</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +761,49 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130446109</v>
+        <v>1330874</v>
       </c>
       <c r="B3" t="n">
-        <v>91794</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,44 +811,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörmyren Öst, Jmt</t>
+          <t>Sidsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509892</v>
+        <v>510174</v>
       </c>
       <c r="R3" t="n">
-        <v>6956310</v>
+        <v>6956139</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2012-11-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2012-11-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,71 +879,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130448983</v>
+        <v>130446110</v>
       </c>
       <c r="B4" t="n">
-        <v>78992</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510086</v>
+        <v>509881</v>
       </c>
       <c r="R4" t="n">
-        <v>6956190</v>
+        <v>6956321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +965,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,6 +991,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1018,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130446098</v>
+        <v>130446111</v>
       </c>
       <c r="B5" t="n">
-        <v>78992</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509854</v>
+        <v>509946</v>
       </c>
       <c r="R5" t="n">
-        <v>6956341</v>
+        <v>6956346</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1099,11 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1107,6 +1117,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130446099</v>
+        <v>80555282</v>
       </c>
       <c r="B6" t="n">
-        <v>78992</v>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,40 +1160,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörmyren Öst, Jmt</t>
+          <t>Norra Sverige, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509927</v>
+        <v>510218</v>
       </c>
       <c r="R6" t="n">
-        <v>6956285</v>
+        <v>6956032</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,12 +1214,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2019-08-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2019-08-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,34 +1238,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130448984</v>
+        <v>130448977</v>
       </c>
       <c r="B7" t="n">
-        <v>78992</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510208</v>
+        <v>510238</v>
       </c>
       <c r="R7" t="n">
-        <v>6956132</v>
+        <v>6956067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,6 +1345,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1336,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130448980</v>
+        <v>130448978</v>
       </c>
       <c r="B8" t="n">
-        <v>79825</v>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510014</v>
+        <v>509918</v>
       </c>
       <c r="R8" t="n">
-        <v>6956212</v>
+        <v>6956264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,6 +1466,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1442,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130446102</v>
+        <v>130446098</v>
       </c>
       <c r="B9" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,10 +1536,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510080</v>
+        <v>509854</v>
       </c>
       <c r="R9" t="n">
-        <v>6956202</v>
+        <v>6956341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446103</v>
+        <v>130446099</v>
       </c>
       <c r="B10" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510124</v>
+        <v>509927</v>
       </c>
       <c r="R10" t="n">
-        <v>6956199</v>
+        <v>6956285</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130448977</v>
+        <v>130446100</v>
       </c>
       <c r="B11" t="n">
-        <v>83215</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,21 +1721,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510238</v>
+        <v>509937</v>
       </c>
       <c r="R11" t="n">
-        <v>6956067</v>
+        <v>6956282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,21 +1799,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1775,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130448986</v>
+        <v>130446101</v>
       </c>
       <c r="B12" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510108</v>
+        <v>510076</v>
       </c>
       <c r="R12" t="n">
-        <v>6956164</v>
+        <v>6956239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,12 +1884,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130448987</v>
+        <v>130446102</v>
       </c>
       <c r="B13" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510052</v>
+        <v>510080</v>
       </c>
       <c r="R13" t="n">
-        <v>6956201</v>
+        <v>6956202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,12 +1990,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130448988</v>
+        <v>130446103</v>
       </c>
       <c r="B14" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510000</v>
+        <v>510124</v>
       </c>
       <c r="R14" t="n">
-        <v>6956229</v>
+        <v>6956199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,12 +2096,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446100</v>
+        <v>130448983</v>
       </c>
       <c r="B15" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509937</v>
+        <v>510086</v>
       </c>
       <c r="R15" t="n">
-        <v>6956282</v>
+        <v>6956190</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,12 +2202,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,10 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130448979</v>
+        <v>130448984</v>
       </c>
       <c r="B16" t="n">
-        <v>79825</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,21 +2251,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509857</v>
+        <v>510208</v>
       </c>
       <c r="R16" t="n">
-        <v>6956348</v>
+        <v>6956132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2349,7 @@
         <v>130448985</v>
       </c>
       <c r="B17" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130448981</v>
+        <v>130448986</v>
       </c>
       <c r="B18" t="n">
-        <v>58037</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,50 +2463,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510001</v>
+        <v>510108</v>
       </c>
       <c r="R18" t="n">
-        <v>6956229</v>
+        <v>6956164</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2500,17 +2528,13 @@
           <t>2025-12-30</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2534,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446110</v>
+        <v>130448987</v>
       </c>
       <c r="B19" t="n">
-        <v>79235</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,21 +2569,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2572,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509881</v>
+        <v>510052</v>
       </c>
       <c r="R19" t="n">
-        <v>6956321</v>
+        <v>6956201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,17 +2626,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,21 +2647,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2660,10 +2664,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446089</v>
+        <v>130448988</v>
       </c>
       <c r="B20" t="n">
-        <v>79825</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2671,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509854</v>
+        <v>510000</v>
       </c>
       <c r="R20" t="n">
-        <v>6956342</v>
+        <v>6956229</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,12 +2732,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,6 +2767,568 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130448981</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>510001</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6956229</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130446089</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>509854</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6956342</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130448979</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>509857</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6956348</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130448980</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>510014</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6956212</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130448982</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>510029</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6956233</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62925-2025 artfynd.xlsx
+++ b/artfynd/A 62925-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446109</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1330874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446110</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80555282</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448978</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1601,6 +1641,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446098</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,6 +1752,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446099</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1813,6 +1863,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446100</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1919,6 +1974,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446101</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2025,6 +2085,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446102</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446103</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448983</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2343,6 +2418,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448984</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2449,6 +2529,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448985</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2555,6 +2640,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448986</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2661,6 +2751,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448987</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2767,6 +2862,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448988</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2890,6 +2990,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448981</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2996,6 +3101,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446089</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3102,6 +3212,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448979</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3208,6 +3323,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448980</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3329,8 +3449,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>